--- a/desc/sample_multi_sheet_import.xlsx
+++ b/desc/sample_multi_sheet_import.xlsx
@@ -19,13 +19,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Noto Sans JP"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans JP"/>
+      <color rgb="0092400E"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Noto Sans JP"/>
@@ -38,12 +49,17 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -82,15 +98,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -458,179 +481,197 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ケース説明</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>新規ユーザーがメールアドレスで会員登録し、本人確認・審査を経てアカウントを開設するフロー。</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
           <t>ステージ名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>担当チーム</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>確認チーム</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="38" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>メールアドレス確認</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>入力フォームのバリデーション。重複チェック・形式確認。</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>フロントエンドチーム</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>QAチーム</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>会員情報入力</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>氏名・住所・生年月日等の個人情報入力フォーム表示。</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>フロントエンドチーム</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>QAチーム</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>本人確認書類アップロード</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>身分証明書（運転免許証・マイナンバー等）のアップロード・OCR読取。</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>バックエンドチーム</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>セキュリティチーム</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>審査・承認処理</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>管理者による申請内容の最終確認・承認。不備がある場合は差し戻し。</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>オペレーションチーム</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>経理チーム</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>アカウント開設完了通知</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>承認後にウェルカムメール送信。マイページへのログイン案内を含む。</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>バックエンドチーム</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>QAチーム</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:E1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -641,179 +682,197 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ケース説明</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>購入者からの返品申請を受け付け、商品検品・返金額計算・クレジット返金処理を行うフロー。</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
           <t>ステージ名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>担当チーム</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>確認チーム</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="38" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>返品申請受付</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>返品理由・商品状態・注文番号をWebフォームで受付。</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>フロントエンドチーム</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>QAチーム</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>返品商品の検品</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>届いた返品商品の状態確認・写真記録。不良品か使用済みかを判定。</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>オペレーションチーム</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>経理チーム</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>返金額の計算</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>商品価格から送料・手数料を控除した返金額を算出。</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>経理チーム</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>経理チーム</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>クレジット返金処理</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>カード会社への返金申請。承認後3〜5営業日で反映。</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>決済チーム</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>経理チーム</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>返金完了通知</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>返金完了メールをユーザーへ送信。返金明細・完了日を記載。</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>バックエンドチーム</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>QAチーム</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:E1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -824,179 +883,197 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ケース説明</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>保有ポイントを使って交換カタログから商品を選び、発送手配・完了通知を行うフロー。</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
           <t>ステージ名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>担当チーム</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>確認チーム</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="38" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>ポイント残高確認</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>交換可能ポイント数・有効期限を取得して画面表示。</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>バックエンドチーム</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>QAチーム</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>交換商品の選択</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>交換カタログから商品選択。必要ポイント数と在庫をリアルタイム確認。</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>フロントエンドチーム</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>QAチーム</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>交換申請・ポイント引落</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>選択商品のポイントをアカウントから即時引き落とし。</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>バックエンドチーム</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>経理チーム</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>発送手配</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>倉庫システムへ発送指示を連携。送り状番号を取得・登録。</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>オペレーションチーム</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>QAチーム</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>発送完了通知</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>追跡番号付きの発送完了メールをユーザーへ送信。</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>バックエンドチーム</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>QAチーム</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:E1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/desc/sample_multi_sheet_import.xlsx
+++ b/desc/sample_multi_sheet_import.xlsx
@@ -481,14 +481,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -505,6 +506,7 @@
       <c r="C1" s="3" t="n"/>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -529,6 +531,11 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>確認内容</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
           <t>期限</t>
         </is>
       </c>
@@ -556,6 +563,11 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>入力値が正しい形式であること。重複ユーザーが存在しないこと。</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>2026-07-05</t>
         </is>
       </c>
@@ -583,6 +595,11 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
+          <t>必須項目がすべて入力されていること。住所の郵便番号自動補完が動作すること。</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
           <t>2026-07-08</t>
         </is>
       </c>
@@ -610,6 +627,11 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>書類画像が鮮明であること。OCR読取結果と入力情報が一致すること。有効期限内であること。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>2026-07-10</t>
         </is>
       </c>
@@ -637,6 +659,11 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
+          <t>申請内容に虚偽がないこと。反社チェックが完了していること。</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
           <t>2026-07-12</t>
         </is>
       </c>
@@ -664,13 +691,18 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>メールが正常に届くこと。ログインURLが正しいこと。初期パスワードが設定されていること。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -682,14 +714,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -706,6 +739,7 @@
       <c r="C1" s="3" t="n"/>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -730,6 +764,11 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>確認内容</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
           <t>期限</t>
         </is>
       </c>
@@ -757,6 +796,11 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>申請フォームが正常に送信されること。注文番号の存在確認が行われること。</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
@@ -784,6 +828,11 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
+          <t>商品状態が記録されていること。写真が添付されていること。判定結果が入力されていること。</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
@@ -811,6 +860,11 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>返金額の計算式が正しいこと。控除項目が明細に記載されていること。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>2026-07-11</t>
         </is>
       </c>
@@ -838,6 +892,11 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
+          <t>返金申請がカード会社に送信されていること。取引IDが記録されていること。</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
           <t>2026-07-14</t>
         </is>
       </c>
@@ -865,13 +924,18 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>メールに返金額・返金日・明細が含まれていること。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -883,14 +947,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -907,6 +972,7 @@
       <c r="C1" s="3" t="n"/>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -931,6 +997,11 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>確認内容</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
           <t>期限</t>
         </is>
       </c>
@@ -958,6 +1029,11 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>残高が正確に表示されること。有効期限が近いポイントが優先表示されること。</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>2026-07-07</t>
         </is>
       </c>
@@ -985,6 +1061,11 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
+          <t>在庫切れ商品が選択不可になっていること。必要ポイント数が正しく表示されること。</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
           <t>2026-07-10</t>
         </is>
       </c>
@@ -1012,6 +1093,11 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>ポイントが正確に引き落とされていること。残高が更新されていること。二重引き落としがないこと。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>2026-07-12</t>
         </is>
       </c>
@@ -1039,6 +1125,11 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
+          <t>倉庫システムへの連携が完了していること。送り状番号が登録されていること。</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
           <t>2026-07-15</t>
         </is>
       </c>
@@ -1066,13 +1157,18 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>追跡URLが有効であること。メール内の商品名・配送先が正しいこと。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>2026-07-18</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
